--- a/resources/survey_data/castelnuovo/case.xlsx
+++ b/resources/survey_data/castelnuovo/case.xlsx
@@ -17,9 +17,10 @@
     <sheet name="Photos" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Connections" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Openings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="MasonryTypes" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Measured" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="_lists" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet name="Vulnerabilities" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="MasonryTypes" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Measured" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="_lists" sheetId="14" state="hidden" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -201,122 +202,17 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Name, the same as the IFC material</t>
+        <t>Facade whose wall has it</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Description</t>
+        <t>FMO vulnerability</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: unit dimensions</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: unit shape</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: unit material</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: mortar quality</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: horizontal joints</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: vertical joints</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>MQI category: wall connections</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for unit dimensions</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for unit shape</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for unit material</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for mortar quality</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for horizontal joints</t>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for vertical joints</t>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
-      <text>
-        <t>Evidence for wall connections</t>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
-      <text>
-        <t>General evidence (optional)</t>
-      </text>
-    </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
-      <text>
-        <t>Assumptions and caveats, one per line</t>
-      </text>
-    </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
-      <text>
-        <t>Mass density (HMO has no rule for it)</t>
-      </text>
-    </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
-      <text>
-        <t>Source of the density</t>
-      </text>
-    </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
-      <text>
-        <t>Code category it is compared with (optional)</t>
-      </text>
-    </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
-      <text>
-        <t>Note on the comparison (optional)</t>
-      </text>
-    </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
-      <text>
-        <t>Lower variant, as parameter=value; ... (optional)</t>
-      </text>
-    </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
-      <text>
-        <t>Upper variant, as parameter=value; ... (optional)</t>
+        <t>What shows it, and its source</t>
       </text>
     </comment>
   </commentList>
@@ -331,6 +227,136 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
+        <t>Name, the same as the IFC material</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Description</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: unit dimensions</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: unit shape</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: unit material</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: mortar quality</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: horizontal joints</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: vertical joints</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>MQI category: wall connections</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for unit dimensions</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for unit shape</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for unit material</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for mortar quality</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for horizontal joints</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for vertical joints</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Evidence for wall connections</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>General evidence (optional)</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>Assumptions and caveats, one per line</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>Mass density (HMO has no rule for it)</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>Source of the density</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>Code category it is compared with (optional)</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>Note on the comparison (optional)</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
+      <text>
+        <t>Lower variant, as parameter=value; ... (optional)</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0" shapeId="0">
+      <text>
+        <t>Upper variant, as parameter=value; ... (optional)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment13.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>openBIMtoFEM</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
         <t>Masonry type</t>
       </text>
     </comment>
@@ -589,6 +615,11 @@
         <t>Name of its masonry type (MasonryTypes)</t>
       </text>
     </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>GlobalIds of its IFC elements, separated by ; (set by the editor)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -606,7 +637,7 @@
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Facade it shows</t>
+        <t>Facades it shows, separated by ;; empty means the aggregate</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
@@ -616,17 +647,27 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
+        <t>Caption (optional)</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
         <t>ISO date and time</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>Activity it was taken in</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>Who took it; empty means the people of the activity</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Source and licence, for photographs taken from a publication</t>
       </text>
     </comment>
   </commentList>
@@ -1013,7 +1054,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>The masonry aggregate of Castelnuovo di Porto described with the Historic Survey (HSV), Historic Structure (HSTO) and Historic Masonry (HMO) ontologies: the survey and its documents, the façades and their walls, and the mechanical properties of the masonry derived by a reasoner from the observed construction features.</t>
+          <t>The masonry aggregate of Castelnuovo di Porto described with the Historic Survey (HSV), Historic Structure (HSTO), Historic Masonry (HMO) and Failure Mechanism (FMO) ontologies: the survey and its documents, the façades and their walls, the mechanical properties of the masonry derived by a reasoner from the observed construction features, and the behaviour of the walls.</t>
         </is>
       </c>
     </row>
@@ -1186,6 +1227,48 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>facade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>vulnerability</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=_lists!$L$2:$L$9</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1709,7 +1792,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1758,13 +1841,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,6 +1906,11 @@
           <t>yes/no</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>vulnerability</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1880,6 +1968,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1937,6 +2030,11 @@
           <t>no</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1989,6 +2087,11 @@
           <t>Tie</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateChains</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -2011,6 +2114,11 @@
           <t>Document</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateCurbstone</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="C6" t="inlineStr">
@@ -2023,6 +2131,11 @@
           <t>Publication</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="C7" t="inlineStr">
@@ -2035,6 +2148,11 @@
           <t>BuildingInformationModel</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ExcessiveSlenderness</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="C8" t="inlineStr">
@@ -2042,11 +2160,21 @@
           <t>squared_hard_stone</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>OpeningsNearIntersections</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
           <t>irregular_hard_stone</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PresenceOfHorizontalThrust</t>
         </is>
       </c>
     </row>
@@ -3152,13 +3280,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3182,6 +3311,11 @@
           <t>masonry_type</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>elements</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3204,6 +3338,7 @@
           <t>Tufelli_masonry_typeC</t>
         </is>
       </c>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3226,6 +3361,7 @@
           <t>Tufelli_masonry_typeD</t>
         </is>
       </c>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3248,6 +3384,7 @@
           <t>Tufelli_masonry_typeB</t>
         </is>
       </c>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3270,6 +3407,7 @@
           <t>Tufelli_masonry_typeB</t>
         </is>
       </c>
+      <c r="E5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3292,6 +3430,7 @@
           <t>Tufelli_masonry_typeD</t>
         </is>
       </c>
+      <c r="E6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3314,6 +3453,7 @@
           <t>Tufelli_masonry_typeA</t>
         </is>
       </c>
+      <c r="E7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3336,6 +3476,7 @@
           <t>Tufelli_masonry_typeD</t>
         </is>
       </c>
+      <c r="E8" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3349,7 +3490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3358,6 +3499,8 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3378,17 +3521,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>taken</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>activity</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acquired_by</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
         </is>
       </c>
     </row>
@@ -3408,17 +3561,19 @@
           <t>A-417/417_a/WhatsApp Image 2023-06-01 at 14.50.43 (1).jpeg</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:43</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3436,17 +3591,19 @@
           <t>A-417/417_a/WhatsApp Image 2023-06-01 at 14.50.44 (1).jpeg</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:44</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3464,17 +3621,19 @@
           <t>A-417/417_a/WhatsApp Image 2023-06-01 at 14.50.44.jpeg</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:44</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3492,17 +3651,19 @@
           <t>A-417/417_a/WhatsApp Image 2023-06-01 at 14.50.45 (1).jpeg</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:45</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3520,17 +3681,19 @@
           <t>A-417/417_a/WhatsApp Image 2023-06-01 at 14.50.45.jpeg</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:45</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3548,17 +3711,19 @@
           <t>A-417/417_a/WhatsApp Image 2023-06-01 at 14.50.46.jpeg</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:46</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3576,17 +3741,19 @@
           <t>A-417/417_a/WhatsApp Image 2023-06-01 at 14.51.48.jpeg</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:51:48</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3604,17 +3771,19 @@
           <t>A-417/417_a/WhatsApp Image 2023-06-01 at 14.51.49 (1).jpeg</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:51:49</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3632,17 +3801,19 @@
           <t>A-417/417_a/WhatsApp Image 2023-06-01 at 14.51.49.jpeg</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:51:49</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3660,17 +3831,19 @@
           <t>A-417/417_a/WhatsApp Image 2023-06-01 at 14.51.50 (1).jpeg</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:51:50</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3688,17 +3861,19 @@
           <t>A-417/417_a/WhatsApp Image 2023-06-01 at 14.51.50.jpeg</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:51:50</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3717,12 +3892,14 @@
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3741,12 +3918,14 @@
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3764,17 +3943,19 @@
           <t>A-417/417_b/WhatsApp Image 2023-06-01 at 14.51.52 (1).jpeg</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:51:52</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3792,17 +3973,19 @@
           <t>A-417/417_b/WhatsApp Image 2023-06-01 at 14.51.52.jpeg</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:51:52</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3820,17 +4003,19 @@
           <t>A-417/417_c/WhatsApp Image 2023-06-01 at 14.50.40.jpeg</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:40</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3848,17 +4033,19 @@
           <t>A-417/417_c/WhatsApp Image 2023-06-01 at 14.50.41 (1).jpeg</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:41</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3876,17 +4063,19 @@
           <t>A-417/417_c/WhatsApp Image 2023-06-01 at 14.50.41.jpeg</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:41</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3904,17 +4093,19 @@
           <t>A-417/417_c/WhatsApp Image 2023-06-01 at 14.50.42 (1).jpeg</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:42</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3932,17 +4123,19 @@
           <t>A-417/417_c/WhatsApp Image 2023-06-01 at 14.50.42.jpeg</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:42</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3960,17 +4153,19 @@
           <t>A-417/417_c/WhatsApp Image 2023-06-01 at 14.50.43.jpeg</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:43</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3988,17 +4183,19 @@
           <t>A-417/417_c/WhatsApp Image 2023-06-01 at 14.50.55 (1).jpeg</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:55</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4016,17 +4213,19 @@
           <t>A-417/417_c/WhatsApp Image 2023-06-01 at 14.51.51.jpeg</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:51:51</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4045,12 +4244,14 @@
         </is>
       </c>
       <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4069,12 +4270,14 @@
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4093,12 +4296,14 @@
         </is>
       </c>
       <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4116,17 +4321,19 @@
           <t>A-418/418-a/WhatsApp Image 2023-06-01 at 14.50.47 (1).jpeg</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:47</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4144,17 +4351,19 @@
           <t>A-418/418-a/WhatsApp Image 2023-06-01 at 14.50.47.jpeg</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:47</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -4172,17 +4381,19 @@
           <t>A-418/418-a/WhatsApp Image 2023-06-01 at 14.50.48 (1).jpeg</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:48</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -4200,17 +4411,19 @@
           <t>A-418/418-a/WhatsApp Image 2023-06-01 at 14.50.48.jpeg</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:48</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -4228,17 +4441,19 @@
           <t>A-418/418-a/WhatsApp Image 2023-06-01 at 14.50.49 (1).jpeg</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:49</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -4256,17 +4471,19 @@
           <t>A-418/418b/WhatsApp Image 2023-06-01 at 14.51.53 (1).jpeg</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:51:53</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -4284,17 +4501,19 @@
           <t>A-418/418b/WhatsApp Image 2023-06-01 at 14.51.53.jpeg</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:51:53</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -4312,17 +4531,19 @@
           <t>A-418/418b/WhatsApp Image 2023-06-01 at 14.51.54 (1).jpeg</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:51:54</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -4340,17 +4561,19 @@
           <t>A-418/418b/WhatsApp Image 2023-06-01 at 14.51.54.jpeg</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:51:54</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -4368,17 +4591,19 @@
           <t>A-418/418b/WhatsApp Image 2023-06-01 at 14.51.55.jpeg</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:51:55</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -4396,17 +4621,19 @@
           <t>A-419/a419/WhatsApp Image 2023-06-01 at 14.50.49.jpeg</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:49</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4424,17 +4651,19 @@
           <t>A-419/a419/WhatsApp Image 2023-06-01 at 14.50.50 (1).jpeg</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:50</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -4452,17 +4681,19 @@
           <t>A-419/a419/WhatsApp Image 2023-06-01 at 14.50.50.jpeg</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:50</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4480,17 +4711,19 @@
           <t>A-419/a419/WhatsApp Image 2023-06-01 at 14.50.51 (1).jpeg</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:51</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4508,17 +4741,19 @@
           <t>A-419/a419/WhatsApp Image 2023-06-01 at 14.50.51.jpeg</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:51</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4536,17 +4771,19 @@
           <t>A-420/a420/WhatsApp Image 2023-06-01 at 14.50.52 (1).jpeg</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:52</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4564,17 +4801,19 @@
           <t>A-420/a420/WhatsApp Image 2023-06-01 at 14.50.52.jpeg</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:52</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4592,17 +4831,19 @@
           <t>A-420/a420/WhatsApp Image 2023-06-01 at 14.50.53 (1).jpeg</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:53</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4620,17 +4861,19 @@
           <t>A-420/a420/WhatsApp Image 2023-06-01 at 14.50.53.jpeg</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:53</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4648,17 +4891,19 @@
           <t>A-420/a420/WhatsApp Image 2023-06-01 at 14.50.54 (1).jpeg</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:54</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4676,17 +4921,19 @@
           <t>A-420/a420/WhatsApp Image 2023-06-01 at 14.50.54.jpeg</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:54</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4704,17 +4951,19 @@
           <t>A-420/a420/WhatsApp Image 2023-06-01 at 14.50.55.jpeg</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>2023-06-01T14:50:55</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>PhotographicCampaign</t>
         </is>
       </c>
-      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/survey_data/castelnuovo/case.xlsx
+++ b/resources/survey_data/castelnuovo/case.xlsx
@@ -1232,7 +1232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1254,6 +1254,601 @@
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417a</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Timber floors alla romana documented for the aggregate as a whole (Section 8.2.3); no stiffening of the floors observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417a</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Historic tuff masonry with timber floors and roofs; no curb beam visible at the top of the walls in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417a</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateCurbstone</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>No curb beam visible at the floor levels in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417a</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>No tie-rod anchor plates visible at the top of the walls in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417a</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateChains</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>No tie-rod anchor plates visible at the floor levels in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417b</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Timber floors alla romana documented for the aggregate as a whole (Section 8.2.3); no stiffening of the floors observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417b</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Historic tuff masonry with timber floors and roofs; no curb beam visible at the top of the walls in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417b</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateCurbstone</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>No curb beam visible at the floor levels in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417b</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>No tie-rod anchor plates visible at the top of the walls in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417b</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateChains</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>No tie-rod anchor plates visible at the floor levels in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417c</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Timber floors alla romana documented for the aggregate as a whole (Section 8.2.3); no stiffening of the floors observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417c</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Historic tuff masonry with timber floors and roofs; no curb beam visible at the top of the walls in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417c</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateCurbstone</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>No curb beam visible at the floor levels in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417c</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>No tie-rod anchor plates visible at the top of the walls in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Facade_417c</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateChains</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>No tie-rod anchor plates visible at the floor levels in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Facade_418a</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Timber floors alla romana documented for the aggregate as a whole (Section 8.2.3); no stiffening of the floors observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Facade_418a</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Historic tuff masonry with timber floors and roofs; no curb beam visible at the top of the walls in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Facade_418a</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateCurbstone</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>No curb beam visible at the floor levels in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Facade_418a</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>No tie-rod anchor plates visible at the top of the walls in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Facade_418a</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateChains</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>No tie-rod anchor plates visible at the floor levels in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Facade_418b</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Timber floors alla romana documented for the aggregate as a whole (Section 8.2.3); no stiffening of the floors observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Facade_418b</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Historic tuff masonry with timber floors and roofs; no curb beam visible at the top of the walls in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Facade_418b</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateCurbstone</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>No curb beam visible at the floor levels in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Facade_418b</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>No tie-rod anchor plates visible at the top of the walls in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Facade_418b</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateChains</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>No tie-rod anchor plates visible at the floor levels in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Facade_419</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Timber floors alla romana documented for the aggregate as a whole (Section 8.2.3); no stiffening of the floors observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Facade_419</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Historic tuff masonry with timber floors and roofs; no curb beam visible at the top of the walls in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Facade_419</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateCurbstone</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>No curb beam visible at the floor levels in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Facade_419</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>No tie-rod anchor plates visible at the top of the walls in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Facade_419</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateChains</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>No tie-rod anchor plates visible at the floor levels in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Facade_420</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>DeformableFloors</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Timber floors alla romana documented for the aggregate as a whole (Section 8.2.3); no stiffening of the floors observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Facade_420</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopCurbstone</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Historic tuff masonry with timber floors and roofs; no curb beam visible at the top of the walls in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Facade_420</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateCurbstone</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>No curb beam visible at the floor levels in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Facade_420</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfTopChains</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>No tie-rod anchor plates visible at the top of the walls in the survey photographs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Facade_420</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>AbsenceOfIntermediateChains</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>No tie-rod anchor plates visible at the floor levels in the survey photographs.</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3933,11 @@
           <t>Tufelli_masonry_typeC</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>112HIUctr2yw5OqZgr3kla; 112HIUctr2yw5OqZgr3kXe; 112HIUctr2yw5OqZgr3kYs; 112HIUctr2yw5OqZgr3kaS; 3c8HC29$17vfNgcUAdeh3J; 3c8HC29$17vfNgcUAdeh3I; 3c8HC29$17vfNgcUAdeh3H; 3c8HC29$17vfNgcUAdeh3G; 1FujFrxrb7ouwnZEeyzKU0; 2HmFfYHsL2OPZKrO6tYf$1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3361,7 +3960,11 @@
           <t>Tufelli_masonry_typeD</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>3c8HC29$17vfNgcUAdeh01; 3c8HC29$17vfNgcUAdeh00; 3c8HC29$17vfNgcUAdeh07; 3c8HC29$17vfNgcUAdeh06; 0QfxonMDT2A8cO_M93$yye; 0QfxonMDT2A8cO_M93$yp8</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3384,7 +3987,11 @@
           <t>Tufelli_masonry_typeB</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2XzZEtRJH75fftbZbcqwO2; 2XzZEtRJH75fftbZbcqwH8; 2XzZEtRJH75fftbZbcqwJ5; 07H4IE3N17quz_RDvElapV</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3407,7 +4014,11 @@
           <t>Tufelli_masonry_typeB</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2XzZEtRJH75fftbZbcqwCR; 2XzZEtRJH75fftbZbcqwCB; 0CvVHHujLB8fkhpCAWbiT3; 1HfLPk$M547Aaac6ue3X37; 2tiNzAytfCwQOKJzMPcwjv</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3430,7 +4041,11 @@
           <t>Tufelli_masonry_typeD</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2XzZEtRJH75fftbZbcqwNS; 1HfLPk$M547Aaac6ue3X0L; 2QEzj1Im5478gG84LIeYU2; 2QEzj1Im5478gG84LIeYTv</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3453,7 +4068,11 @@
           <t>Tufelli_masonry_typeA</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0GisCWViz2PeUrBi4wgVRW; 112HIUctr2yw5OqZgr3kPn; 112HIUctr2yw5OqZgr3kPe; 112HIUctr2yw5OqZgr3ksc; 0M1S9S_Qr3IPBMDqinoabk; 37gWW_uGL459BrbCF$MAq8; 2XzZEtRJH75fftbZbcqwY_; 2XzZEtRJH75fftbZbcqwZb; 2SDwapJ$z32OyuRGCv33co; 3_wR1BNVfAMeWWIaQS4y2L; 3_wR1BNVfAMeWWIaQS4ySL; 3_wR1BNVfAMeWWIaQS4yS9; 0F0gJxCaz6DgMK0q1JiO7L; 1aMTge6B9DK9$RHbrOwo4u</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3476,7 +4095,11 @@
           <t>Tufelli_masonry_typeD</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0GisCWViz2PeUrBi4wgVUt; 0GisCWViz2PeUrBi4wgUZp; 0GisCWViz2PeUrBi4wgUdW; 0GisCWViz2PeUrBi4wgUa5; 112HIUctr2yw5OqZgr3kPo; 112HIUctr2yw5OqZgr3kPp; 112HIUctr2yw5OqZgr3kPi; 112HIUctr2yw5OqZgr3kPj; 112HIUctr2yw5OqZgr3kPf; 112HIUctr2yw5OqZgr3kPg; 112HIUctr2yw5OqZgr3kPh; 112HIUctr2yw5OqZgr3kPa</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/survey_data/castelnuovo/case.xlsx
+++ b/resources/survey_data/castelnuovo/case.xlsx
@@ -3935,7 +3935,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>112HIUctr2yw5OqZgr3kla; 112HIUctr2yw5OqZgr3kXe; 112HIUctr2yw5OqZgr3kYs; 112HIUctr2yw5OqZgr3kaS; 3c8HC29$17vfNgcUAdeh3J; 3c8HC29$17vfNgcUAdeh3I; 3c8HC29$17vfNgcUAdeh3H; 3c8HC29$17vfNgcUAdeh3G; 1FujFrxrb7ouwnZEeyzKU0; 2HmFfYHsL2OPZKrO6tYf$1</t>
+          <t>112HIUctr2yw5OqZgr3kla; 112HIUctr2yw5OqZgr3kXe; 112HIUctr2yw5OqZgr3kYs; 112HIUctr2yw5OqZgr3kaS; 3c8HC29$17vfNgcUAdeh3J; 3c8HC29$17vfNgcUAdeh3I; 3c8HC29$17vfNgcUAdeh3H; 3c8HC29$17vfNgcUAdeh3G; 1FujFrxrb7ouwnZEeyzKU0; 2HmFfYHsL2OPZKrO6tYf$1; 3c8HC29$17vfNgcUAdeh01; 3c8HC29$17vfNgcUAdeh00; 3c8HC29$17vfNgcUAdeh07; 3c8HC29$17vfNgcUAdeh06; 0QfxonMDT2A8cO_M93$yye; 0QfxonMDT2A8cO_M93$yp8</t>
         </is>
       </c>
     </row>
@@ -3960,11 +3960,7 @@
           <t>Tufelli_masonry_typeD</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>3c8HC29$17vfNgcUAdeh01; 3c8HC29$17vfNgcUAdeh00; 3c8HC29$17vfNgcUAdeh07; 3c8HC29$17vfNgcUAdeh06; 0QfxonMDT2A8cO_M93$yye; 0QfxonMDT2A8cO_M93$yp8</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4016,7 +4012,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2XzZEtRJH75fftbZbcqwCR; 2XzZEtRJH75fftbZbcqwCB; 0CvVHHujLB8fkhpCAWbiT3; 1HfLPk$M547Aaac6ue3X37; 2tiNzAytfCwQOKJzMPcwjv</t>
+          <t>2XzZEtRJH75fftbZbcqwCR; 2XzZEtRJH75fftbZbcqwCB; 0CvVHHujLB8fkhpCAWbiT3; 1HfLPk$M547Aaac6ue3X37; 2tiNzAytfCwQOKJzMPcwjv; 2XzZEtRJH75fftbZbcqwNS; 1HfLPk$M547Aaac6ue3X0L; 2QEzj1Im5478gG84LIeYU2; 2QEzj1Im5478gG84LIeYTv</t>
         </is>
       </c>
     </row>
@@ -4041,11 +4037,7 @@
           <t>Tufelli_masonry_typeD</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2XzZEtRJH75fftbZbcqwNS; 1HfLPk$M547Aaac6ue3X0L; 2QEzj1Im5478gG84LIeYU2; 2QEzj1Im5478gG84LIeYTv</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">

--- a/resources/survey_data/castelnuovo/case.xlsx
+++ b/resources/survey_data/castelnuovo/case.xlsx
@@ -3930,12 +3930,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Tufelli_masonry_typeC</t>
+          <t>Tufelli_masonry_typeD</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>112HIUctr2yw5OqZgr3kla; 112HIUctr2yw5OqZgr3kXe; 112HIUctr2yw5OqZgr3kYs; 112HIUctr2yw5OqZgr3kaS; 3c8HC29$17vfNgcUAdeh3J; 3c8HC29$17vfNgcUAdeh3I; 3c8HC29$17vfNgcUAdeh3H; 3c8HC29$17vfNgcUAdeh3G; 1FujFrxrb7ouwnZEeyzKU0; 2HmFfYHsL2OPZKrO6tYf$1; 3c8HC29$17vfNgcUAdeh01; 3c8HC29$17vfNgcUAdeh00; 3c8HC29$17vfNgcUAdeh07; 3c8HC29$17vfNgcUAdeh06; 0QfxonMDT2A8cO_M93$yye; 0QfxonMDT2A8cO_M93$yp8</t>
+          <t>0GisCWViz2PeUrBi4wgVUt; 0GisCWViz2PeUrBi4wgUZp; 0GisCWViz2PeUrBi4wgUdW; 0GisCWViz2PeUrBi4wgUa5; 112HIUctr2yw5OqZgr3kPo; 112HIUctr2yw5OqZgr3kPp; 112HIUctr2yw5OqZgr3kPi; 112HIUctr2yw5OqZgr3kPj; 112HIUctr2yw5OqZgr3kPf; 112HIUctr2yw5OqZgr3kPg; 112HIUctr2yw5OqZgr3kPh; 112HIUctr2yw5OqZgr3kPa</t>
         </is>
       </c>
     </row>
@@ -3980,14 +3980,10 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Tufelli_masonry_typeB</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2XzZEtRJH75fftbZbcqwO2; 2XzZEtRJH75fftbZbcqwH8; 2XzZEtRJH75fftbZbcqwJ5; 07H4IE3N17quz_RDvElapV</t>
-        </is>
-      </c>
+          <t>Tufelli_masonry_typeD</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4007,12 +4003,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Tufelli_masonry_typeB</t>
+          <t>Tufelli_masonry_typeA</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2XzZEtRJH75fftbZbcqwCR; 2XzZEtRJH75fftbZbcqwCB; 0CvVHHujLB8fkhpCAWbiT3; 1HfLPk$M547Aaac6ue3X37; 2tiNzAytfCwQOKJzMPcwjv; 2XzZEtRJH75fftbZbcqwNS; 1HfLPk$M547Aaac6ue3X0L; 2QEzj1Im5478gG84LIeYU2; 2QEzj1Im5478gG84LIeYTv</t>
+          <t>0GisCWViz2PeUrBi4wgVRW; 112HIUctr2yw5OqZgr3kPn; 112HIUctr2yw5OqZgr3kPe; 112HIUctr2yw5OqZgr3ksc; 0M1S9S_Qr3IPBMDqinoabk; 37gWW_uGL459BrbCF$MAq8; 2XzZEtRJH75fftbZbcqwY_; 2XzZEtRJH75fftbZbcqwZb; 2SDwapJ$z32OyuRGCv33co; 3_wR1BNVfAMeWWIaQS4y2L; 3_wR1BNVfAMeWWIaQS4ySL; 3_wR1BNVfAMeWWIaQS4yS9; 0F0gJxCaz6DgMK0q1JiO7L; 1aMTge6B9DK9$RHbrOwo4u</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4030,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Tufelli_masonry_typeD</t>
+          <t>Tufelli_masonry_typeA</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
@@ -4057,12 +4053,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Tufelli_masonry_typeA</t>
+          <t>Tufelli_masonry_typeD</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0GisCWViz2PeUrBi4wgVRW; 112HIUctr2yw5OqZgr3kPn; 112HIUctr2yw5OqZgr3kPe; 112HIUctr2yw5OqZgr3ksc; 0M1S9S_Qr3IPBMDqinoabk; 37gWW_uGL459BrbCF$MAq8; 2XzZEtRJH75fftbZbcqwY_; 2XzZEtRJH75fftbZbcqwZb; 2SDwapJ$z32OyuRGCv33co; 3_wR1BNVfAMeWWIaQS4y2L; 3_wR1BNVfAMeWWIaQS4ySL; 3_wR1BNVfAMeWWIaQS4yS9; 0F0gJxCaz6DgMK0q1JiO7L; 1aMTge6B9DK9$RHbrOwo4u</t>
+          <t>2XzZEtRJH75fftbZbcqwCR; 2XzZEtRJH75fftbZbcqwCB; 0CvVHHujLB8fkhpCAWbiT3; 1HfLPk$M547Aaac6ue3X37; 2tiNzAytfCwQOKJzMPcwjv; 2XzZEtRJH75fftbZbcqwNS; 1HfLPk$M547Aaac6ue3X0L; 2QEzj1Im5478gG84LIeYU2; 2QEzj1Im5478gG84LIeYTv; 2XzZEtRJH75fftbZbcqwO2; 2XzZEtRJH75fftbZbcqwH8; 2XzZEtRJH75fftbZbcqwJ5; 07H4IE3N17quz_RDvElapV</t>
         </is>
       </c>
     </row>
@@ -4084,12 +4080,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Tufelli_masonry_typeD</t>
+          <t>Tufelli_masonry_typeC</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0GisCWViz2PeUrBi4wgVUt; 0GisCWViz2PeUrBi4wgUZp; 0GisCWViz2PeUrBi4wgUdW; 0GisCWViz2PeUrBi4wgUa5; 112HIUctr2yw5OqZgr3kPo; 112HIUctr2yw5OqZgr3kPp; 112HIUctr2yw5OqZgr3kPi; 112HIUctr2yw5OqZgr3kPj; 112HIUctr2yw5OqZgr3kPf; 112HIUctr2yw5OqZgr3kPg; 112HIUctr2yw5OqZgr3kPh; 112HIUctr2yw5OqZgr3kPa</t>
+          <t>112HIUctr2yw5OqZgr3kla; 112HIUctr2yw5OqZgr3kXe; 112HIUctr2yw5OqZgr3kYs; 112HIUctr2yw5OqZgr3kaS; 3c8HC29$17vfNgcUAdeh3J; 3c8HC29$17vfNgcUAdeh3I; 3c8HC29$17vfNgcUAdeh3H; 3c8HC29$17vfNgcUAdeh3G; 1FujFrxrb7ouwnZEeyzKU0; 2HmFfYHsL2OPZKrO6tYf$1; 3c8HC29$17vfNgcUAdeh01; 3c8HC29$17vfNgcUAdeh00; 3c8HC29$17vfNgcUAdeh07; 3c8HC29$17vfNgcUAdeh06; 0QfxonMDT2A8cO_M93$yye; 0QfxonMDT2A8cO_M93$yp8</t>
         </is>
       </c>
     </row>

--- a/resources/survey_data/castelnuovo/case.xlsx
+++ b/resources/survey_data/castelnuovo/case.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Project" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Organisations" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="People" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Activities" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Documents" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Units" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Facades" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Photos" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Connections" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Openings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Vulnerabilities" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="MasonryTypes" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Measured" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="_lists" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organisations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="People" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Activities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facades" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Photos" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Connections" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Openings" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vulnerabilities" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MasonryTypes" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Measured" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="14" state="hidden" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -237,37 +237,37 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: unit dimensions</t>
+        <t>Morphological characteristic: unit dimensions</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: unit shape</t>
+        <t>Morphological characteristic: unit shape</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: unit material</t>
+        <t>Morphological characteristic: unit material</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: mortar quality</t>
+        <t>Morphological characteristic: mortar quality</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: horizontal joints</t>
+        <t>Morphological characteristic: horizontal joints</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: vertical joints</t>
+        <t>Morphological characteristic: vertical joints</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>MQI category: wall connections</t>
+        <t>Morphological characteristic: wall connections</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
@@ -337,12 +337,12 @@
     </comment>
     <comment ref="W1" authorId="0" shapeId="0">
       <text>
-        <t>Lower variant, as parameter=value; ... (optional)</t>
+        <t>Lower variant, as characteristic=category; ... (optional)</t>
       </text>
     </comment>
     <comment ref="X1" authorId="0" shapeId="0">
       <text>
-        <t>Upper variant, as parameter=value; ... (optional)</t>
+        <t>Upper variant, as characteristic=category; ... (optional)</t>
       </text>
     </comment>
   </commentList>
@@ -1854,7 +1854,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$L$2:$L$9</formula1>
     </dataValidation>
   </dataValidations>
@@ -2360,25 +2360,25 @@
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$C$2:$C$9</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$D$2:$D$5</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$E$2:$E$4</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$F$2:$F$4</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$G$2:$G$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -3669,7 +3669,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$H$2:$H$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -3857,10 +3857,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$I$2:$I$4</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$K$2:$K$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -5633,7 +5633,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
       <formula1>=_lists!$J$2:$J$4</formula1>
     </dataValidation>
   </dataValidations>
